--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N1_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N1_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>50.3392640194061</v>
+        <v>8.180130403153491</v>
       </c>
       <c r="D2" t="n">
-        <v>50.23579375479373</v>
+        <v>8.163316485153981</v>
       </c>
       <c r="E2" t="n">
-        <v>1.115294302125051</v>
+        <v>0.1812353240953213</v>
       </c>
       <c r="F2" t="n">
-        <v>1.19254207696391</v>
+        <v>0.1937880875066353</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>52.5698526236562</v>
+        <v>8.542601051344134</v>
       </c>
       <c r="D3" t="n">
-        <v>52.62087790872155</v>
+        <v>8.550892660167252</v>
       </c>
       <c r="E3" t="n">
-        <v>1.115294302125051</v>
+        <v>0.1812353240953213</v>
       </c>
       <c r="F3" t="n">
-        <v>1.19254207696391</v>
+        <v>0.1937880875066353</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
